--- a/data/releases/v4.0/china_city_entity_master_V4.0.xlsx
+++ b/data/releases/v4.0/china_city_entity_master_V4.0.xlsx
@@ -17657,7 +17657,7 @@
         </is>
       </c>
       <c r="O236" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P236" t="inlineStr"/>
       <c r="Q236" t="inlineStr"/>
@@ -25667,7 +25667,7 @@
         <v>1988</v>
       </c>
       <c r="I346" t="n">
-        <v>1997</v>
+        <v>1996</v>
       </c>
       <c r="J346" t="inlineStr">
         <is>
@@ -25687,11 +25687,11 @@
       </c>
       <c r="N346" t="inlineStr">
         <is>
-          <t>1987-1987 [not_established]; 1988-1997 黔江地区; 1998-2026 [abolished]</t>
+          <t>1987-1987 [not_established]; 1988-1996 黔江地区; 1997-2026 [abolished]</t>
         </is>
       </c>
       <c r="O346" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P346" t="inlineStr">
         <is>
@@ -26153,7 +26153,7 @@
         </is>
       </c>
       <c r="O352" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P352" t="inlineStr">
         <is>
@@ -26230,7 +26230,7 @@
         </is>
       </c>
       <c r="O353" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P353" t="inlineStr">
         <is>
@@ -26307,7 +26307,7 @@
         </is>
       </c>
       <c r="O354" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P354" t="inlineStr">
         <is>
@@ -26384,7 +26384,7 @@
         </is>
       </c>
       <c r="O355" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P355" t="inlineStr">
         <is>
@@ -26461,7 +26461,7 @@
         </is>
       </c>
       <c r="O356" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P356" t="inlineStr">
         <is>
@@ -26538,7 +26538,7 @@
         </is>
       </c>
       <c r="O357" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P357" t="inlineStr">
         <is>
@@ -26846,7 +26846,7 @@
         </is>
       </c>
       <c r="O361" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P361" t="inlineStr">
         <is>
@@ -26923,7 +26923,7 @@
         </is>
       </c>
       <c r="O362" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P362" t="inlineStr">
         <is>

--- a/data/releases/v4.0/china_city_entity_master_V4.0.xlsx
+++ b/data/releases/v4.0/china_city_entity_master_V4.0.xlsx
@@ -11091,7 +11091,7 @@
         </is>
       </c>
       <c r="O146" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P146" t="inlineStr"/>
       <c r="Q146" t="inlineStr"/>
@@ -16124,7 +16124,7 @@
         </is>
       </c>
       <c r="O215" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P215" t="inlineStr"/>
       <c r="Q215" t="inlineStr"/>
@@ -16197,7 +16197,7 @@
         </is>
       </c>
       <c r="O216" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P216" t="inlineStr"/>
       <c r="Q216" t="inlineStr"/>

--- a/data/releases/v4.0/china_city_entity_master_V4.0.xlsx
+++ b/data/releases/v4.0/china_city_entity_master_V4.0.xlsx
@@ -6715,7 +6715,7 @@
         </is>
       </c>
       <c r="O86" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P86" t="inlineStr"/>
       <c r="Q86" t="inlineStr"/>
@@ -6788,7 +6788,7 @@
         </is>
       </c>
       <c r="O87" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P87" t="inlineStr"/>
       <c r="Q87" t="inlineStr"/>
@@ -11018,7 +11018,7 @@
         </is>
       </c>
       <c r="O145" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P145" t="inlineStr"/>
       <c r="Q145" t="inlineStr"/>
@@ -11160,7 +11160,7 @@
         </is>
       </c>
       <c r="O147" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P147" t="inlineStr"/>
       <c r="Q147" t="inlineStr"/>
@@ -14299,7 +14299,7 @@
         </is>
       </c>
       <c r="O190" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P190" t="inlineStr"/>
       <c r="Q190" t="inlineStr"/>
@@ -15978,7 +15978,7 @@
         </is>
       </c>
       <c r="O213" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P213" t="inlineStr"/>
       <c r="Q213" t="inlineStr"/>
@@ -16051,7 +16051,7 @@
         </is>
       </c>
       <c r="O214" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P214" t="inlineStr"/>
       <c r="Q214" t="inlineStr"/>
@@ -16270,7 +16270,7 @@
         </is>
       </c>
       <c r="O217" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P217" t="inlineStr"/>
       <c r="Q217" t="inlineStr"/>
@@ -16854,7 +16854,7 @@
         </is>
       </c>
       <c r="O225" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P225" t="inlineStr"/>
       <c r="Q225" t="inlineStr"/>
@@ -17438,7 +17438,7 @@
         </is>
       </c>
       <c r="O233" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P233" t="inlineStr"/>
       <c r="Q233" t="inlineStr"/>
